--- a/output/pdf_financials_xlsx/ALMA.xlsx
+++ b/output/pdf_financials_xlsx/ALMA.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.122716</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.16998</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.162193</v>
       </c>
     </row>
     <row r="93">
@@ -2323,13 +2323,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.269662</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.973101</v>
+        <v>0.6509819999999999</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>2.102499</v>
+        <v>2.050766</v>
       </c>
     </row>
     <row r="119">
@@ -3003,7 +3003,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>0.122716</v>
       </c>
@@ -3534,7 +3538,11 @@
           <t>Exploration and evaluation expenditures (Note 5)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>-0.269662</v>
       </c>

--- a/output/pdf_financials_xlsx/ALMA.xlsx
+++ b/output/pdf_financials_xlsx/ALMA.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>8.1e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.209944</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.448835</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>8.1e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.209944</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.448835</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.055229</v>
+        <v>0.055148</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.228402</v>
+        <v>0.018458</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.502503</v>
+        <v>0.053668</v>
       </c>
     </row>
     <row r="49">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/ALMA.xlsx
+++ b/output/pdf_financials_xlsx/ALMA.xlsx
@@ -3633,7 +3633,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.3905</v>
       </c>
@@ -3844,7 +3848,11 @@
           <t>Fair value of warrants issued with private placement (Note 6)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
